--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487068_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487068_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. JUSTO ANTOLIN</t>
+          <t>A. GUTIEZ SALGADO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2626</v>
+        <v>2.9949</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2803</v>
+        <v>1.3975</v>
       </c>
       <c r="F2" t="n">
-        <v>2.543</v>
+        <v>1.5974</v>
       </c>
       <c r="G2" t="n">
-        <v>1.2691</v>
+        <v>-0.717</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.7772</v>
+        <v>0.6967</v>
       </c>
       <c r="I2" t="n">
-        <v>2.0464</v>
+        <v>-1.4137</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7019</v>
+        <v>-0.651</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.5434</v>
+        <v>0.1965</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2453</v>
+        <v>-0.8475</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5673</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2338</v>
+        <v>0.5002</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8011</v>
+        <v>-0.5662</v>
       </c>
       <c r="P2" t="n">
-        <v>1.158</v>
+        <v>1.7371</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.965</v>
+        <v>-0.193</v>
       </c>
       <c r="R2" t="n">
-        <v>2.1231</v>
+        <v>1.9301</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1646</v>
+        <v>-0.3434</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0172</v>
+        <v>-0.2145</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1474</v>
+        <v>-0.1289</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>2.3182</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.4559</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.1377</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. GUTIEZ SALGADO</t>
+          <t>A. JUSTO ANTOLIN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1114</v>
+        <v>2.1744</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1393</v>
+        <v>-0.5024</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9721</v>
+        <v>2.6768</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.717</v>
+        <v>1.2691</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6967</v>
+        <v>-0.7772</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.4137</v>
+        <v>2.0464</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.651</v>
+        <v>0.7019</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1965</v>
+        <v>-0.5434</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.8475</v>
+        <v>1.2453</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.06610000000000001</v>
+        <v>0.5673</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5002</v>
+        <v>-0.2338</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5662</v>
+        <v>0.8011</v>
       </c>
       <c r="P3" t="n">
-        <v>1.7371</v>
+        <v>1.158</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.193</v>
+        <v>-0.965</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9301</v>
+        <v>2.1231</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.2268</v>
+        <v>-0.2528</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.4726</v>
+        <v>-0.2393</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2458</v>
+        <v>-0.0136</v>
       </c>
       <c r="V3" t="n">
-        <v>2.3182</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.4559</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1377</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2461</v>
+        <v>1.0587</v>
       </c>
       <c r="E4" t="n">
         <v>0.1527</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0934</v>
+        <v>0.906</v>
       </c>
       <c r="G4" t="n">
         <v>0.5248</v>
@@ -766,13 +766,13 @@
         <v>0.193</v>
       </c>
       <c r="S4" t="n">
-        <v>0.158</v>
+        <v>-0.0294</v>
       </c>
       <c r="T4" t="n">
         <v>-0.1785</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3364</v>
+        <v>0.149</v>
       </c>
       <c r="V4" t="n">
         <v>0.3704</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0391</v>
+        <v>0.3421</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4435</v>
+        <v>1.8803</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.4043</v>
+        <v>-1.5382</v>
       </c>
       <c r="G5" t="n">
         <v>1.4523</v>
@@ -844,13 +844,13 @@
         <v>1.3511</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8018</v>
+        <v>0.1048</v>
       </c>
       <c r="T5" t="n">
-        <v>1.3035</v>
+        <v>0.7403</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5017</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>-1.4079</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9468</v>
+        <v>0.237</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.2452</v>
+        <v>-3.4094</v>
       </c>
       <c r="F6" t="n">
-        <v>3.2984</v>
+        <v>3.6464</v>
       </c>
       <c r="G6" t="n">
         <v>1.9073</v>
@@ -922,13 +922,13 @@
         <v>3.4741</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.5151</v>
+        <v>-1.3312</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.2215</v>
+        <v>-0.3856</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.2936</v>
+        <v>-0.9456</v>
       </c>
       <c r="V6" t="n">
         <v>2.1701</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.6687</v>
+        <v>-0.6048</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.3466</v>
+        <v>-1.4702</v>
       </c>
       <c r="F7" t="n">
-        <v>0.678</v>
+        <v>0.8653999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>0.9958</v>
@@ -1000,13 +1000,13 @@
         <v>1.9301</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2565</v>
+        <v>-0.1927</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.4581</v>
+        <v>-0.5816</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2016</v>
+        <v>0.389</v>
       </c>
       <c r="V7" t="n">
         <v>-1.4079</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0856</v>
+        <v>-1.694</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.3535</v>
+        <v>-3.0154</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2679</v>
+        <v>1.3214</v>
       </c>
       <c r="G8" t="n">
         <v>-2.2245</v>
@@ -1078,13 +1078,13 @@
         <v>2.1231</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0192</v>
+        <v>-0.6276</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6848</v>
+        <v>-0.3467</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3345</v>
+        <v>-0.2809</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ ORTEGA</t>
+          <t>P. MOLINA MATA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6491</v>
+        <v>-1.8604</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.476</v>
+        <v>-1.5379</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8269</v>
+        <v>-0.3225</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.8798</v>
+        <v>-0.7669</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.0547</v>
+        <v>2.3019</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.825</v>
+        <v>-3.0689</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.7467</v>
+        <v>-0.1406</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9474</v>
+        <v>1.8215</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.7993</v>
+        <v>-1.9621</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1331</v>
+        <v>-0.6263</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1074</v>
+        <v>0.4804</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0257</v>
+        <v>-1.1067</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.965</v>
+        <v>1.158</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.0881</v>
+        <v>-1.158</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1231</v>
+        <v>2.3161</v>
       </c>
       <c r="S9" t="n">
-        <v>2.6036</v>
+        <v>-1.0235</v>
       </c>
       <c r="T9" t="n">
-        <v>2.0729</v>
+        <v>-0.2393</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5306999999999999</v>
+        <v>-0.7843</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.4079</v>
+        <v>-1.228</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.6938</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. MOLINA MATA</t>
+          <t>A. KARATZAS LACABEX</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7517</v>
+        <v>-3.2238</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2954</v>
+        <v>-5.8478</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4564</v>
+        <v>2.624</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7669</v>
+        <v>-2.8991</v>
       </c>
       <c r="H10" t="n">
-        <v>2.3019</v>
+        <v>1.5806</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.0689</v>
+        <v>-4.4797</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1406</v>
+        <v>-3.4464</v>
       </c>
       <c r="K10" t="n">
         <v>1.8215</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.9621</v>
+        <v>-5.268</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6263</v>
+        <v>0.5474</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4804</v>
+        <v>-0.2409</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1067</v>
+        <v>0.7883</v>
       </c>
       <c r="P10" t="n">
-        <v>1.158</v>
+        <v>1.7371</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.158</v>
+        <v>-1.9301</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3161</v>
+        <v>3.6672</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.9149</v>
+        <v>-0.7383</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9967</v>
+        <v>-0.7571</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9181</v>
+        <v>0.0188</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.228</v>
+        <v>-1.3234</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.228</v>
+        <v>-1.6093</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. KARATZAS LACABEX</t>
+          <t>A. FERNANDEZ ORTEGA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.707</v>
+        <v>-4.3019</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.1436</v>
+        <v>-4.7808</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4366</v>
+        <v>0.4789</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.8991</v>
+        <v>-2.8798</v>
       </c>
       <c r="H11" t="n">
-        <v>1.5806</v>
+        <v>-1.0547</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.4797</v>
+        <v>-1.825</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.4464</v>
+        <v>-2.7467</v>
       </c>
       <c r="K11" t="n">
-        <v>1.8215</v>
+        <v>-0.9474</v>
       </c>
       <c r="L11" t="n">
-        <v>-5.268</v>
+        <v>-1.7993</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5474</v>
+        <v>-0.1331</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2409</v>
+        <v>-0.1074</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7883</v>
+        <v>-0.0257</v>
       </c>
       <c r="P11" t="n">
-        <v>1.7371</v>
+        <v>-0.965</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9301</v>
+        <v>-3.0881</v>
       </c>
       <c r="R11" t="n">
-        <v>3.6672</v>
+        <v>2.1231</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.2216</v>
+        <v>0.9508</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.053</v>
+        <v>0.7681</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1686</v>
+        <v>0.1827</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.3234</v>
+        <v>-1.4079</v>
       </c>
       <c r="W11" t="n">
         <v>0.2859</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.6093</v>
+        <v>-1.6938</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.149699999999999</v>
+        <v>-4.877800000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-20.4051</v>
+        <v>-17.1334</v>
       </c>
       <c r="F12" t="n">
         <v>12.2556</v>
@@ -1375,7 +1375,7 @@
         <v>0.1039</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2965999999999999</v>
+        <v>0.2965999999999998</v>
       </c>
       <c r="O12" t="n">
         <v>-0.1928</v>
@@ -1390,13 +1390,13 @@
         <v>21.231</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.7553</v>
+        <v>-3.4833</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.706</v>
+        <v>-1.4342</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.0494</v>
+        <v>-2.049399999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-1.916399999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.9861</v>
+        <v>9.002800000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>4.037</v>
+        <v>5.4389</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9491</v>
+        <v>3.5638</v>
       </c>
       <c r="G13" t="n">
         <v>6.5275</v>
@@ -1468,13 +1468,13 @@
         <v>2.3161</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8514</v>
+        <v>1.1653</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9677</v>
+        <v>0.4343</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1163</v>
+        <v>0.731</v>
       </c>
       <c r="V13" t="n">
         <v>4.012</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.5288</v>
+        <v>4.1537</v>
       </c>
       <c r="E14" t="n">
         <v>2.15</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3788</v>
+        <v>2.0037</v>
       </c>
       <c r="G14" t="n">
         <v>5.4481</v>
@@ -1546,13 +1546,13 @@
         <v>2.7021</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1568</v>
+        <v>1.7817</v>
       </c>
       <c r="T14" t="n">
         <v>0.6187</v>
       </c>
       <c r="U14" t="n">
-        <v>1.538</v>
+        <v>1.1629</v>
       </c>
       <c r="V14" t="n">
         <v>-1.7251</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8897</v>
+        <v>3.0955</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9798</v>
+        <v>2.0786</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9098000000000001</v>
+        <v>1.0169</v>
       </c>
       <c r="G15" t="n">
         <v>2.1828</v>
@@ -1624,13 +1624,13 @@
         <v>1.3511</v>
       </c>
       <c r="S15" t="n">
-        <v>2.7418</v>
+        <v>1.9476</v>
       </c>
       <c r="T15" t="n">
-        <v>2.4166</v>
+        <v>1.5153</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3252</v>
+        <v>0.4323</v>
       </c>
       <c r="V15" t="n">
         <v>-1.228</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.194</v>
+        <v>2.1996</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4018</v>
+        <v>-0.1003</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7923</v>
+        <v>2.2999</v>
       </c>
       <c r="G16" t="n">
         <v>1.4307</v>
@@ -1702,13 +1702,13 @@
         <v>1.7371</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3616</v>
+        <v>0.3672</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4807</v>
+        <v>-0.0214</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.119</v>
+        <v>0.3886</v>
       </c>
       <c r="V16" t="n">
         <v>-0.3704</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0167</v>
+        <v>0.3436</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.238</v>
+        <v>-0.9375</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2547</v>
+        <v>1.2811</v>
       </c>
       <c r="G17" t="n">
         <v>0.4437</v>
@@ -1780,13 +1780,13 @@
         <v>0.772</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.234</v>
+        <v>0.0929</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4164</v>
+        <v>-0.116</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1824</v>
+        <v>0.2089</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0097</v>
+        <v>-0.5357</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.1542</v>
+        <v>-4.0541</v>
       </c>
       <c r="F18" t="n">
-        <v>3.1445</v>
+        <v>3.5183</v>
       </c>
       <c r="G18" t="n">
         <v>-3.2152</v>
@@ -1858,13 +1858,13 @@
         <v>1.9301</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2056</v>
+        <v>0.6795</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5076000000000001</v>
+        <v>-0.4075</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7131999999999999</v>
+        <v>1.087</v>
       </c>
       <c r="V18" t="n">
         <v>1.228</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0905</v>
+        <v>-0.5429</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0257</v>
+        <v>-1.8255</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9352</v>
+        <v>1.2826</v>
       </c>
       <c r="G19" t="n">
         <v>-0.491</v>
@@ -1936,13 +1936,13 @@
         <v>0.772</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4065</v>
+        <v>0.1411</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4759</v>
+        <v>-0.2756</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0694</v>
+        <v>0.4167</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. AMBROSONI ÁLVAREZ</t>
+          <t>A. GARCIA NAVALON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4536</v>
+        <v>-1.3534</v>
       </c>
       <c r="E20" t="n">
-        <v>-6.4878</v>
+        <v>-2.0871</v>
       </c>
       <c r="F20" t="n">
-        <v>4.0342</v>
+        <v>0.7337</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.8098</v>
+        <v>-2.9262</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5238</v>
+        <v>-2.5078</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.286</v>
+        <v>-0.4184</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.5583</v>
+        <v>-2.1658</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6983</v>
+        <v>-1.506</v>
       </c>
       <c r="L20" t="n">
-        <v>-3.2566</v>
+        <v>-0.6597</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7485000000000001</v>
+        <v>-0.7604</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2222</v>
+        <v>-1.0018</v>
       </c>
       <c r="O20" t="n">
-        <v>1.9707</v>
+        <v>0.2413</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.158</v>
+        <v>1.9301</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.0881</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>1.9301</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0575</v>
+        <v>0.2145</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.4132</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>1.3556</v>
+        <v>0.1358</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5717</v>
+        <v>-0.5717</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5717</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. GARCIA NAVALON</t>
+          <t>F. AMBROSONI ÁLVAREZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5957</v>
+        <v>-1.6195</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.0885</v>
+        <v>-5.7869</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4928</v>
+        <v>4.1674</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.9262</v>
+        <v>-1.8098</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.5078</v>
+        <v>-0.5238</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4184</v>
+        <v>-1.286</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.1658</v>
+        <v>-2.5583</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.506</v>
+        <v>0.6983</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6597</v>
+        <v>-3.2566</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7604</v>
+        <v>0.7485000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0018</v>
+        <v>-1.2222</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2413</v>
+        <v>1.9707</v>
       </c>
       <c r="P21" t="n">
-        <v>1.9301</v>
+        <v>-1.158</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.0881</v>
       </c>
       <c r="R21" t="n">
         <v>1.9301</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0278</v>
+        <v>0.7766</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9227</v>
+        <v>-0.7122000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1051</v>
+        <v>1.4888</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5717</v>
+        <v>0.5717</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.5717</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5717</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3161</v>
+        <v>-4.5912</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.8299</v>
+        <v>-7.1317</v>
       </c>
       <c r="F22" t="n">
-        <v>2.5138</v>
+        <v>2.5405</v>
       </c>
       <c r="G22" t="n">
         <v>-4.2528</v>
@@ -2170,13 +2170,13 @@
         <v>1.9301</v>
       </c>
       <c r="S22" t="n">
-        <v>2.8667</v>
+        <v>1.5917</v>
       </c>
       <c r="T22" t="n">
-        <v>2.2368</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6299</v>
+        <v>0.6566</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>8.149700000000001</v>
+        <v>10.1525</v>
       </c>
       <c r="E23" t="n">
-        <v>-12.2555</v>
+        <v>-12.2556</v>
       </c>
       <c r="F23" t="n">
-        <v>20.4052</v>
+        <v>22.4079</v>
       </c>
       <c r="G23" t="n">
         <v>3.337800000000001</v>
@@ -2227,10 +2227,10 @@
         <v>-0.2968000000000002</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1930000000000003</v>
+        <v>0.1929999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>3.441800000000001</v>
+        <v>3.4418</v>
       </c>
       <c r="N23" t="n">
         <v>-10.385</v>
@@ -2248,13 +2248,13 @@
         <v>17.3708</v>
       </c>
       <c r="S23" t="n">
-        <v>6.755299999999999</v>
+        <v>8.758100000000001</v>
       </c>
       <c r="T23" t="n">
         <v>2.0493</v>
       </c>
       <c r="U23" t="n">
-        <v>4.7059</v>
+        <v>6.7086</v>
       </c>
       <c r="V23" t="n">
         <v>1.916499999999999</v>
